--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -299,7 +299,7 @@
     <t>Specimen.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,7 +588,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|Group|Device|Substance|http://hl7.org/fhir/us/core/StructureDefinition/us-core-location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/substance-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -632,7 +632,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -651,7 +651,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -940,7 +940,7 @@
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/substance-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1447,7 +1447,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="182.72265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-specimen-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-specimen-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="364">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,13 +714,39 @@
     <t>Specimen.collection.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Specimen.collection.extension:collectionPriority</t>
+  </si>
+  <si>
+    <t>collectionPriority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/specimen-collectionPriority-314e}
+</t>
+  </si>
+  <si>
+    <t>The urgency of sample collection</t>
+  </si>
+  <si>
+    <t>The urgency of sample collection, such as STAT, ASAP, ASAP-ED, ROUTINE, ROUTINE-AM, etc.…</t>
+  </si>
+  <si>
+    <t>Specimen.collection.extension:specialHandling</t>
+  </si>
+  <si>
+    <t>specialHandling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/specimen-specialHandling-314e}
+</t>
+  </si>
+  <si>
+    <t>Special handling during the collection, transport, or storage of the specimen</t>
+  </si>
+  <si>
+    <t>Special handling during the collection, transport, or storage of the specimen.</t>
   </si>
   <si>
     <t>Specimen.collection.modifierExtension</t>
@@ -905,6 +931,12 @@
   </si>
   <si>
     <t>Specimen.processing.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Specimen.processing.modifierExtension</t>
@@ -1434,12 +1466,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.90625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.90625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.61328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -3807,7 +3839,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3829,14 +3861,12 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3873,19 +3903,17 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3900,7 +3928,7 @@
         <v>135</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -3911,46 +3939,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -3998,7 +4024,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4007,13 +4033,13 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>135</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
@@ -4024,12 +4050,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4038,7 +4066,7 @@
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4047,16 +4075,16 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4107,68 +4135,72 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>236</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>238</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4222,30 +4254,30 @@
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>127</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4268,13 +4300,13 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4325,7 +4357,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4340,21 +4372,21 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4374,16 +4406,16 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4434,7 +4466,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4449,21 +4481,21 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4483,16 +4515,16 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4519,13 +4551,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -4543,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4558,21 +4590,21 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4595,17 +4627,15 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4630,11 +4660,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -4652,7 +4684,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4667,21 +4699,21 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4701,23 +4733,19 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4741,13 +4769,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -4765,7 +4793,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4780,21 +4808,21 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4805,7 +4833,7 @@
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4817,15 +4845,17 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4850,13 +4880,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -4874,13 +4902,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -4889,21 +4917,21 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4923,19 +4951,23 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -4959,13 +4991,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -4983,7 +5015,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4995,28 +5027,28 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5035,17 +5067,15 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>222</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5094,7 +5124,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5106,10 +5136,10 @@
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
@@ -5120,46 +5150,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5207,22 +5233,22 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5233,21 +5259,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5259,15 +5285,17 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5316,22 +5344,22 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -5342,42 +5370,46 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5401,13 +5433,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5425,22 +5457,22 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -5451,10 +5483,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5465,7 +5497,7 @@
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5477,7 +5509,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>295</v>
+        <v>216</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>296</v>
@@ -5534,13 +5566,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -5555,15 +5587,15 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5586,13 +5618,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5619,13 +5651,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -5643,7 +5675,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5658,7 +5690,7 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>241</v>
+        <v>178</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5669,10 +5701,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5695,13 +5727,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>210</v>
+        <v>305</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5752,7 +5784,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5767,21 +5799,21 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5804,13 +5836,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>218</v>
+        <v>312</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5861,7 +5893,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5873,10 +5905,10 @@
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -5887,14 +5919,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5913,17 +5945,15 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -5972,7 +6002,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>224</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5984,10 +6014,10 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>220</v>
+        <v>316</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -5998,46 +6028,42 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6085,22 +6111,22 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6111,14 +6137,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6134,18 +6160,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6194,7 +6222,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6206,56 +6234,60 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>315</v>
+        <v>235</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6303,22 +6335,22 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>314</v>
+        <v>237</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>317</v>
+        <v>127</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -6329,10 +6361,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6343,7 +6375,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6352,16 +6384,16 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6388,13 +6420,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6412,13 +6444,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -6427,7 +6459,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -6464,7 +6496,7 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>325</v>
@@ -6542,15 +6574,15 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6573,13 +6605,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>249</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6606,13 +6638,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -6630,7 +6662,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6645,7 +6677,7 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>178</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
@@ -6682,13 +6714,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6715,13 +6747,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -6754,21 +6786,21 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6779,7 +6811,7 @@
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -6788,23 +6820,19 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -6828,11 +6856,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -6850,13 +6880,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -6865,21 +6895,21 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6890,7 +6920,7 @@
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -6902,13 +6932,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>50</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6935,13 +6965,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -6959,13 +6989,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -6974,17 +7004,237 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="B51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>353</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM50">
+  <autoFilter ref="A1:AM52">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6994,7 +7244,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI51">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
